--- a/data/000572_海马汽车_财务数据.xlsx
+++ b/data/000572_海马汽车_财务数据.xlsx
@@ -11614,7 +11614,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>归属于少数股东的综合收益总额</t>
+          <t>minority_common_profit_total</t>
         </is>
       </c>
       <c r="B32" s="3" t="n">
@@ -18714,7 +18714,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC11"/>
+  <dimension ref="A1:AA11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -18744,8 +18744,6 @@
     <col width="16" customWidth="1" min="25" max="25"/>
     <col width="16" customWidth="1" min="26" max="26"/>
     <col width="16" customWidth="1" min="27" max="27"/>
-    <col width="16" customWidth="1" min="28" max="28"/>
-    <col width="16" customWidth="1" min="29" max="29"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -18792,22 +18790,22 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>财务费用率(%)</t>
+          <t>资产负债率(%)</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>资产负债率(%)</t>
+          <t>流动比率</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>流动比率</t>
+          <t>速动比率</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>速动比率</t>
+          <t>产权比率(%)</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
@@ -18817,75 +18815,65 @@
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>应收账款周转天数(天)</t>
+          <t>存货周转率(次)</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>存货周转率(次)</t>
+          <t>总资产周转率(次)</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>存货周转天数(天)</t>
+          <t>流动资产周转率(次)</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>总资产周转率(次)</t>
+          <t>固定资产周转率(次)</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>流动资产周转率(次)</t>
+          <t>营收同比(%)</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>固定资产周转率(次)</t>
+          <t>净利润同比(%)</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>营收同比(%)</t>
+          <t>总资产增长率(%)</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>净利润同比(%)</t>
+          <t>经营现金流/净利润</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>总资产增长率(%)</t>
+          <t>自由现金流(元)</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>经营现金流/净利润</t>
+          <t>现金收入比</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>自由现金流(元)</t>
+          <t>现金流组合</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>现金收入比</t>
+          <t>Altman Z-score</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>现金流组合</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>Altman Z-score</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Z-score判定</t>
         </is>
@@ -18919,58 +18907,52 @@
         <v>6.800246357357291</v>
       </c>
       <c r="I2" s="4" t="inlineStr"/>
-      <c r="J2" s="6" t="n">
-        <v>-0.1761295544624232</v>
-      </c>
-      <c r="K2" s="3" t="n">
+      <c r="J2" s="3" t="n">
         <v>47.02714584020222</v>
       </c>
+      <c r="K2" s="6" t="n">
+        <v>0.7942761345946592</v>
+      </c>
       <c r="L2" s="6" t="n">
-        <v>0.7942761345946592</v>
-      </c>
-      <c r="M2" s="6" t="n">
         <v>0.6002873907316488</v>
+      </c>
+      <c r="M2" s="3" t="n">
+        <v>88.76672544341874</v>
       </c>
       <c r="N2" s="3" t="n">
         <v>6.273744783518518</v>
       </c>
       <c r="O2" s="3" t="n">
-        <v>57.38199630717212</v>
-      </c>
-      <c r="P2" s="3" t="n">
         <v>8.776762646561728</v>
       </c>
+      <c r="P2" s="6" t="n">
+        <v>0.7632745879058138</v>
+      </c>
       <c r="Q2" s="3" t="n">
-        <v>41.01740180259164</v>
-      </c>
-      <c r="R2" s="6" t="n">
-        <v>0.7632745879058138</v>
-      </c>
-      <c r="S2" s="3" t="n">
         <v>2.094085775774159</v>
       </c>
+      <c r="R2" s="4" t="inlineStr"/>
+      <c r="S2" s="4" t="inlineStr"/>
       <c r="T2" s="4" t="inlineStr"/>
       <c r="U2" s="4" t="inlineStr"/>
-      <c r="V2" s="4" t="inlineStr"/>
-      <c r="W2" s="4" t="inlineStr"/>
-      <c r="X2" s="3" t="n">
+      <c r="V2" s="3" t="n">
         <v>27.29956867977059</v>
       </c>
-      <c r="Y2" s="3" t="n">
+      <c r="W2" s="3" t="n">
         <v>-270000000</v>
       </c>
-      <c r="Z2" s="6" t="n">
+      <c r="X2" s="6" t="n">
         <v>0.9091386246198053</v>
       </c>
+      <c r="Y2" s="4" t="inlineStr">
+        <is>
+          <t>+/−/+</t>
+        </is>
+      </c>
+      <c r="Z2" s="3" t="n">
+        <v>1.501379108543367</v>
+      </c>
       <c r="AA2" s="4" t="inlineStr">
-        <is>
-          <t>+/−/+</t>
-        </is>
-      </c>
-      <c r="AB2" s="3" t="n">
-        <v>1.501379108543367</v>
-      </c>
-      <c r="AC2" s="4" t="inlineStr">
         <is>
           <t>危险区</t>
         </is>
@@ -19006,64 +18988,58 @@
       <c r="I3" s="3" t="n">
         <v>4.958311025637819</v>
       </c>
-      <c r="J3" s="6" t="n">
-        <v>0.1204804666320422</v>
-      </c>
-      <c r="K3" s="3" t="n">
+      <c r="J3" s="3" t="n">
         <v>47.64769201544988</v>
       </c>
+      <c r="K3" s="6" t="n">
+        <v>0.9071294559099438</v>
+      </c>
       <c r="L3" s="6" t="n">
-        <v>0.9071294559099438</v>
-      </c>
-      <c r="M3" s="6" t="n">
         <v>0.6948092557848655</v>
+      </c>
+      <c r="M3" s="3" t="n">
+        <v>91.01354620222544</v>
       </c>
       <c r="N3" s="3" t="n">
         <v>4.62205008728401</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>77.88751597271022</v>
-      </c>
-      <c r="P3" s="3" t="n">
         <v>7.788492639838817</v>
       </c>
+      <c r="P3" s="6" t="n">
+        <v>0.5697505182465947</v>
+      </c>
       <c r="Q3" s="3" t="n">
-        <v>46.2220376454577</v>
-      </c>
-      <c r="R3" s="6" t="n">
-        <v>0.5697505182465947</v>
-      </c>
+        <v>1.557409719800563</v>
+      </c>
+      <c r="R3" s="4" t="inlineStr"/>
       <c r="S3" s="3" t="n">
-        <v>1.557409719800563</v>
-      </c>
-      <c r="T3" s="4" t="inlineStr"/>
+        <v>-30.28692965484789</v>
+      </c>
+      <c r="T3" s="3" t="n">
+        <v>-11014.01664095644</v>
+      </c>
       <c r="U3" s="3" t="n">
-        <v>-30.28692965484789</v>
+        <v>-13.21573799318606</v>
       </c>
       <c r="V3" s="3" t="n">
-        <v>-11014.01664095644</v>
+        <v>1.277515970154311</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>-13.21573799318606</v>
-      </c>
-      <c r="X3" s="3" t="n">
-        <v>1.277515970154311</v>
-      </c>
-      <c r="Y3" s="3" t="n">
         <v>-2334000000</v>
       </c>
-      <c r="Z3" s="6" t="n">
+      <c r="X3" s="6" t="n">
         <v>0.869341168732796</v>
       </c>
+      <c r="Y3" s="4" t="inlineStr">
+        <is>
+          <t>−/−/+</t>
+        </is>
+      </c>
+      <c r="Z3" s="3" t="n">
+        <v>1.026599393685639</v>
+      </c>
       <c r="AA3" s="4" t="inlineStr">
-        <is>
-          <t>−/−/+</t>
-        </is>
-      </c>
-      <c r="AB3" s="3" t="n">
-        <v>1.026599393685639</v>
-      </c>
-      <c r="AC3" s="4" t="inlineStr">
         <is>
           <t>危险区</t>
         </is>
@@ -19099,64 +19075,58 @@
       <c r="I4" s="3" t="n">
         <v>12.5001755505845</v>
       </c>
-      <c r="J4" s="6" t="n">
-        <v>0.4969105539930584</v>
-      </c>
-      <c r="K4" s="3" t="n">
+      <c r="J4" s="3" t="n">
         <v>49.58980624890906</v>
       </c>
+      <c r="K4" s="6" t="n">
+        <v>0.5885588558855885</v>
+      </c>
       <c r="L4" s="6" t="n">
-        <v>0.5885588558855885</v>
-      </c>
-      <c r="M4" s="6" t="n">
         <v>0.46002933626696</v>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>98.35554786221222</v>
       </c>
       <c r="N4" s="3" t="n">
         <v>2.931835574417659</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>122.7899692401767</v>
-      </c>
-      <c r="P4" s="3" t="n">
         <v>6.180293031277319</v>
       </c>
+      <c r="P4" s="6" t="n">
+        <v>0.3704197968045209</v>
+      </c>
       <c r="Q4" s="3" t="n">
-        <v>58.24966521459527</v>
-      </c>
-      <c r="R4" s="6" t="n">
-        <v>0.3704197968045209</v>
-      </c>
+        <v>1.120096524935641</v>
+      </c>
+      <c r="R4" s="4" t="inlineStr"/>
       <c r="S4" s="3" t="n">
-        <v>1.120096524935641</v>
-      </c>
-      <c r="T4" s="4" t="inlineStr"/>
+        <v>-47.87717301618665</v>
+      </c>
+      <c r="T4" s="3" t="n">
+        <v>-60.63263026116039</v>
+      </c>
       <c r="U4" s="3" t="n">
-        <v>-47.87717301618665</v>
-      </c>
-      <c r="V4" s="3" t="n">
-        <v>-60.63263026116039</v>
+        <v>-27.44886975242196</v>
+      </c>
+      <c r="V4" s="6" t="n">
+        <v>-0.2151012826974996</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>-27.44886975242196</v>
+        <v>-332000000.0000002</v>
       </c>
       <c r="X4" s="6" t="n">
-        <v>-0.2151012826974996</v>
-      </c>
-      <c r="Y4" s="3" t="n">
-        <v>-332000000.0000002</v>
+        <v>0.9395392166665339</v>
+      </c>
+      <c r="Y4" s="4" t="inlineStr">
+        <is>
+          <t>+/−/−</t>
+        </is>
       </c>
       <c r="Z4" s="6" t="n">
-        <v>0.9395392166665339</v>
+        <v>0.08522307340187707</v>
       </c>
       <c r="AA4" s="4" t="inlineStr">
-        <is>
-          <t>+/−/−</t>
-        </is>
-      </c>
-      <c r="AB4" s="6" t="n">
-        <v>0.08522307340187707</v>
-      </c>
-      <c r="AC4" s="4" t="inlineStr">
         <is>
           <t>危险区</t>
         </is>
@@ -19192,64 +19162,58 @@
       <c r="I5" s="3" t="n">
         <v>4.328657597603859</v>
       </c>
-      <c r="J5" s="6" t="n">
-        <v>0.3787049548403867</v>
-      </c>
-      <c r="K5" s="3" t="n">
+      <c r="J5" s="3" t="n">
         <v>46.66790940441793</v>
       </c>
+      <c r="K5" s="6" t="n">
+        <v>0.6594863297431649</v>
+      </c>
       <c r="L5" s="6" t="n">
-        <v>0.6594863297431649</v>
-      </c>
-      <c r="M5" s="6" t="n">
         <v>0.5412178956089478</v>
+      </c>
+      <c r="M5" s="3" t="n">
+        <v>87.50436910171268</v>
       </c>
       <c r="N5" s="3" t="n">
         <v>4.87880647050442</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>73.78853868798357</v>
-      </c>
-      <c r="P5" s="3" t="n">
         <v>8.73128285514151</v>
       </c>
+      <c r="P5" s="6" t="n">
+        <v>0.4228577474548159</v>
+      </c>
       <c r="Q5" s="3" t="n">
-        <v>41.23105458529615</v>
-      </c>
-      <c r="R5" s="6" t="n">
-        <v>0.4228577474548159</v>
-      </c>
+        <v>1.467304479634032</v>
+      </c>
+      <c r="R5" s="4" t="inlineStr"/>
       <c r="S5" s="3" t="n">
-        <v>1.467304479634032</v>
-      </c>
-      <c r="T5" s="4" t="inlineStr"/>
+        <v>-7.057095019041021</v>
+      </c>
+      <c r="T5" s="3" t="n">
+        <v>104.2939017078253</v>
+      </c>
       <c r="U5" s="3" t="n">
-        <v>-7.057095019041021</v>
-      </c>
-      <c r="V5" s="3" t="n">
-        <v>104.2939017078253</v>
+        <v>-6.36236690521906</v>
+      </c>
+      <c r="V5" s="6" t="n">
+        <v>-0.5968715085569372</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>-6.36236690521906</v>
+        <v>-519263800.0000001</v>
       </c>
       <c r="X5" s="6" t="n">
-        <v>-0.5968715085569372</v>
-      </c>
-      <c r="Y5" s="3" t="n">
-        <v>-519263800.0000001</v>
+        <v>0.8706084012299212</v>
+      </c>
+      <c r="Y5" s="4" t="inlineStr">
+        <is>
+          <t>−/+/+</t>
+        </is>
       </c>
       <c r="Z5" s="6" t="n">
-        <v>0.8706084012299212</v>
+        <v>0.9098958557942045</v>
       </c>
       <c r="AA5" s="4" t="inlineStr">
-        <is>
-          <t>−/+/+</t>
-        </is>
-      </c>
-      <c r="AB5" s="6" t="n">
-        <v>0.9098958557942045</v>
-      </c>
-      <c r="AC5" s="4" t="inlineStr">
         <is>
           <t>危险区</t>
         </is>
@@ -19286,63 +19250,57 @@
         <v>19.35786516953709</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>1.755313740947793</v>
-      </c>
-      <c r="K6" s="3" t="n">
         <v>51.8136403127715</v>
       </c>
+      <c r="K6" s="6" t="n">
+        <v>0.7216264521894548</v>
+      </c>
       <c r="L6" s="6" t="n">
-        <v>0.7216264521894548</v>
-      </c>
-      <c r="M6" s="6" t="n">
         <v>0.6150580875781947</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>107.5276087446473</v>
       </c>
       <c r="N6" s="3" t="n">
         <v>3.873502104957746</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>92.93915176636442</v>
-      </c>
-      <c r="P6" s="3" t="n">
         <v>4.212383467461832</v>
       </c>
-      <c r="Q6" s="3" t="n">
-        <v>85.46230484019009</v>
-      </c>
-      <c r="R6" s="6" t="n">
+      <c r="P6" s="6" t="n">
         <v>0.1379438478467171</v>
       </c>
-      <c r="S6" s="6" t="n">
+      <c r="Q6" s="6" t="n">
         <v>0.4287786863922669</v>
       </c>
-      <c r="T6" s="4" t="inlineStr"/>
+      <c r="R6" s="4" t="inlineStr"/>
+      <c r="S6" s="3" t="n">
+        <v>-70.68639242068832</v>
+      </c>
+      <c r="T6" s="3" t="n">
+        <v>-1413.599860670879</v>
+      </c>
       <c r="U6" s="3" t="n">
-        <v>-70.68639242068832</v>
-      </c>
-      <c r="V6" s="3" t="n">
-        <v>-1413.599860670879</v>
+        <v>-14.17653089756734</v>
+      </c>
+      <c r="V6" s="6" t="n">
+        <v>-0.08578505494831389</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>-14.17653089756734</v>
-      </c>
-      <c r="X6" s="6" t="n">
-        <v>-0.08578505494831389</v>
-      </c>
-      <c r="Y6" s="3" t="n">
         <v>-330000000.0000001</v>
       </c>
-      <c r="Z6" s="3" t="n">
+      <c r="X6" s="3" t="n">
         <v>1.96277598292189</v>
       </c>
+      <c r="Y6" s="4" t="inlineStr">
+        <is>
+          <t>+/−/−</t>
+        </is>
+      </c>
+      <c r="Z6" s="6" t="n">
+        <v>-0.1509887168392503</v>
+      </c>
       <c r="AA6" s="4" t="inlineStr">
-        <is>
-          <t>+/−/−</t>
-        </is>
-      </c>
-      <c r="AB6" s="6" t="n">
-        <v>-0.1509887168392503</v>
-      </c>
-      <c r="AC6" s="4" t="inlineStr">
         <is>
           <t>危险区</t>
         </is>
@@ -19378,64 +19336,58 @@
       <c r="I7" s="3" t="n">
         <v>13.9503767796741</v>
       </c>
-      <c r="J7" s="6" t="n">
-        <v>0.4514601308732579</v>
-      </c>
-      <c r="K7" s="3" t="n">
+      <c r="J7" s="3" t="n">
         <v>44.53515291824053</v>
       </c>
+      <c r="K7" s="6" t="n">
+        <v>0.9239035724658727</v>
+      </c>
       <c r="L7" s="6" t="n">
-        <v>0.9239035724658727</v>
-      </c>
-      <c r="M7" s="6" t="n">
         <v>0.7153645076967761</v>
+      </c>
+      <c r="M7" s="3" t="n">
+        <v>80.29437609841827</v>
       </c>
       <c r="N7" s="3" t="n">
         <v>6.564496932625699</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>54.84045520850072</v>
-      </c>
-      <c r="P7" s="3" t="n">
         <v>3.78257819492887</v>
       </c>
-      <c r="Q7" s="3" t="n">
-        <v>95.17318121344738</v>
-      </c>
-      <c r="R7" s="6" t="n">
+      <c r="P7" s="6" t="n">
         <v>0.2024194575262705</v>
       </c>
-      <c r="S7" s="6" t="n">
+      <c r="Q7" s="6" t="n">
         <v>0.5498572535985026</v>
       </c>
-      <c r="T7" s="4" t="inlineStr"/>
+      <c r="R7" s="4" t="inlineStr"/>
+      <c r="S7" s="3" t="n">
+        <v>28.17802937524987</v>
+      </c>
+      <c r="T7" s="3" t="n">
+        <v>110.5236548344701</v>
+      </c>
       <c r="U7" s="3" t="n">
-        <v>28.17802937524987</v>
+        <v>-10.87098175499567</v>
       </c>
       <c r="V7" s="3" t="n">
-        <v>110.5236548344701</v>
+        <v>1.207924966659969</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>-10.87098175499567</v>
+        <v>-133000000</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>1.207924966659969</v>
-      </c>
-      <c r="Y7" s="3" t="n">
-        <v>-133000000</v>
-      </c>
-      <c r="Z7" s="3" t="n">
         <v>1.161374010053807</v>
       </c>
+      <c r="Y7" s="4" t="inlineStr">
+        <is>
+          <t>+/+/−</t>
+        </is>
+      </c>
+      <c r="Z7" s="6" t="n">
+        <v>0.6880421376774151</v>
+      </c>
       <c r="AA7" s="4" t="inlineStr">
-        <is>
-          <t>+/+/−</t>
-        </is>
-      </c>
-      <c r="AB7" s="6" t="n">
-        <v>0.6880421376774151</v>
-      </c>
-      <c r="AC7" s="4" t="inlineStr">
         <is>
           <t>危险区</t>
         </is>
@@ -19471,64 +19423,58 @@
       <c r="I8" s="3" t="n">
         <v>9.88912091730735</v>
       </c>
-      <c r="J8" s="6" t="n">
-        <v>0.1369970058977072</v>
-      </c>
-      <c r="K8" s="3" t="n">
+      <c r="J8" s="3" t="n">
         <v>52.76940168227265</v>
       </c>
+      <c r="K8" s="6" t="n">
+        <v>0.9231502064147349</v>
+      </c>
       <c r="L8" s="6" t="n">
-        <v>0.9231502064147349</v>
-      </c>
-      <c r="M8" s="6" t="n">
         <v>0.6926008256589393</v>
+      </c>
+      <c r="M8" s="3" t="n">
+        <v>111.7647058823529</v>
       </c>
       <c r="N8" s="3" t="n">
         <v>14.86260235062928</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>24.22186851986642</v>
-      </c>
-      <c r="P8" s="3" t="n">
         <v>4.00505014368421</v>
       </c>
-      <c r="Q8" s="3" t="n">
-        <v>89.88651504593628</v>
-      </c>
-      <c r="R8" s="6" t="n">
+      <c r="P8" s="6" t="n">
         <v>0.327698766108354</v>
       </c>
-      <c r="S8" s="6" t="n">
+      <c r="Q8" s="6" t="n">
         <v>0.7809220924277267</v>
       </c>
-      <c r="T8" s="4" t="inlineStr"/>
+      <c r="R8" s="4" t="inlineStr"/>
+      <c r="S8" s="3" t="n">
+        <v>34.86728585423455</v>
+      </c>
+      <c r="T8" s="3" t="n">
+        <v>-1267.129912326237</v>
+      </c>
       <c r="U8" s="3" t="n">
-        <v>34.86728585423455</v>
-      </c>
-      <c r="V8" s="3" t="n">
-        <v>-1267.129912326237</v>
+        <v>-23.22407700743267</v>
+      </c>
+      <c r="V8" s="6" t="n">
+        <v>-0.1606399923811588</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>-23.22407700743267</v>
+        <v>-41000000.00000003</v>
       </c>
       <c r="X8" s="6" t="n">
-        <v>-0.1606399923811588</v>
-      </c>
-      <c r="Y8" s="3" t="n">
-        <v>-41000000.00000003</v>
+        <v>0.9515689079102025</v>
+      </c>
+      <c r="Y8" s="4" t="inlineStr">
+        <is>
+          <t>+/−/+</t>
+        </is>
       </c>
       <c r="Z8" s="6" t="n">
-        <v>0.9515689079102025</v>
+        <v>-0.47590699429469</v>
       </c>
       <c r="AA8" s="4" t="inlineStr">
-        <is>
-          <t>+/−/+</t>
-        </is>
-      </c>
-      <c r="AB8" s="6" t="n">
-        <v>-0.47590699429469</v>
-      </c>
-      <c r="AC8" s="4" t="inlineStr">
         <is>
           <t>危险区</t>
         </is>
@@ -19564,64 +19510,58 @@
       <c r="I9" s="3" t="n">
         <v>8.322960969184177</v>
       </c>
-      <c r="J9" s="6" t="n">
-        <v>-0.8282714977868139</v>
-      </c>
-      <c r="K9" s="3" t="n">
+      <c r="J9" s="3" t="n">
         <v>62.29619565217392</v>
       </c>
+      <c r="K9" s="6" t="n">
+        <v>0.9539995467935645</v>
+      </c>
       <c r="L9" s="6" t="n">
-        <v>0.9539995467935645</v>
-      </c>
-      <c r="M9" s="6" t="n">
         <v>0.7473374121912532</v>
+      </c>
+      <c r="M9" s="3" t="n">
+        <v>165.2252252252252</v>
       </c>
       <c r="N9" s="3" t="n">
         <v>8.046705054304898</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>44.7388089373804</v>
-      </c>
-      <c r="P9" s="3" t="n">
         <v>3.508435965164835</v>
       </c>
-      <c r="Q9" s="3" t="n">
-        <v>102.6098248833469</v>
-      </c>
-      <c r="R9" s="6" t="n">
+      <c r="P9" s="6" t="n">
         <v>0.3727839183646878</v>
       </c>
-      <c r="S9" s="6" t="n">
+      <c r="Q9" s="6" t="n">
         <v>0.7155544623830266</v>
       </c>
-      <c r="T9" s="4" t="inlineStr"/>
+      <c r="R9" s="4" t="inlineStr"/>
+      <c r="S9" s="3" t="n">
+        <v>7.11673022776461</v>
+      </c>
+      <c r="T9" s="3" t="n">
+        <v>87.35130374391436</v>
+      </c>
       <c r="U9" s="3" t="n">
-        <v>7.11673022776461</v>
+        <v>16.80685605459449</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>87.35130374391436</v>
+        <v>-3.86525468506751</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>16.80685605459449</v>
-      </c>
-      <c r="X9" s="3" t="n">
-        <v>-3.86525468506751</v>
-      </c>
-      <c r="Y9" s="3" t="n">
         <v>528000000</v>
       </c>
+      <c r="X9" s="6" t="n">
+        <v>0.8475040372902788</v>
+      </c>
+      <c r="Y9" s="4" t="inlineStr">
+        <is>
+          <t>+/−/+</t>
+        </is>
+      </c>
       <c r="Z9" s="6" t="n">
-        <v>0.8475040372902788</v>
+        <v>-0.07133572655871934</v>
       </c>
       <c r="AA9" s="4" t="inlineStr">
-        <is>
-          <t>+/−/+</t>
-        </is>
-      </c>
-      <c r="AB9" s="6" t="n">
-        <v>-0.07133572655871934</v>
-      </c>
-      <c r="AC9" s="4" t="inlineStr">
         <is>
           <t>危险区</t>
         </is>
@@ -19658,63 +19598,57 @@
         <v>9.506911897095049</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>1.24103584192785</v>
+        <v>55.11557068625694</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>55.11557068625694</v>
-      </c>
-      <c r="L10" s="3" t="n">
         <v>1.08013816925734</v>
       </c>
-      <c r="M10" s="6" t="n">
+      <c r="L10" s="6" t="n">
         <v>0.9326424870466321</v>
+      </c>
+      <c r="M10" s="3" t="n">
+        <v>122.8434504792332</v>
       </c>
       <c r="N10" s="3" t="n">
         <v>3.042512662005141</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>118.3232544914851</v>
-      </c>
-      <c r="P10" s="3" t="n">
         <v>3.223344243121733</v>
       </c>
-      <c r="Q10" s="3" t="n">
-        <v>111.6852476331688</v>
-      </c>
-      <c r="R10" s="6" t="n">
+      <c r="P10" s="6" t="n">
         <v>0.2743692354964841</v>
       </c>
-      <c r="S10" s="6" t="n">
+      <c r="Q10" s="6" t="n">
         <v>0.4839324351315251</v>
       </c>
-      <c r="T10" s="4" t="inlineStr"/>
+      <c r="R10" s="4" t="inlineStr"/>
+      <c r="S10" s="3" t="n">
+        <v>-30.27900279802994</v>
+      </c>
+      <c r="T10" s="3" t="n">
+        <v>-38.78315859538349</v>
+      </c>
       <c r="U10" s="3" t="n">
-        <v>-30.27900279802994</v>
+        <v>-24.1711956521739</v>
       </c>
       <c r="V10" s="3" t="n">
-        <v>-38.78315859538349</v>
+        <v>2.723614256640072</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>-24.1711956521739</v>
-      </c>
-      <c r="X10" s="3" t="n">
-        <v>2.723614256640072</v>
-      </c>
-      <c r="Y10" s="3" t="n">
         <v>-877000000</v>
       </c>
+      <c r="X10" s="6" t="n">
+        <v>0.977296232232346</v>
+      </c>
+      <c r="Y10" s="4" t="inlineStr">
+        <is>
+          <t>−/+/−</t>
+        </is>
+      </c>
       <c r="Z10" s="6" t="n">
-        <v>0.977296232232346</v>
+        <v>-0.1879291547547463</v>
       </c>
       <c r="AA10" s="4" t="inlineStr">
-        <is>
-          <t>−/+/−</t>
-        </is>
-      </c>
-      <c r="AB10" s="6" t="n">
-        <v>-0.1879291547547463</v>
-      </c>
-      <c r="AC10" s="4" t="inlineStr">
         <is>
           <t>危险区</t>
         </is>
@@ -19751,63 +19685,57 @@
         <v>5.919910368697527</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>1.394356409360616</v>
+        <v>55.25513315714576</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>55.25513315714576</v>
-      </c>
-      <c r="L11" s="3" t="n">
         <v>1.030980392156863</v>
       </c>
-      <c r="M11" s="6" t="n">
+      <c r="L11" s="6" t="n">
         <v>0.8027450980392157</v>
+      </c>
+      <c r="M11" s="3" t="n">
+        <v>123.4893230349841</v>
       </c>
       <c r="N11" s="3" t="n">
         <v>4.617351578526842</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>77.9667724836447</v>
-      </c>
-      <c r="P11" s="3" t="n">
         <v>4.210298723647175</v>
       </c>
-      <c r="Q11" s="3" t="n">
-        <v>85.50462179276194</v>
-      </c>
-      <c r="R11" s="6" t="n">
+      <c r="P11" s="6" t="n">
         <v>0.3522379632761905</v>
       </c>
-      <c r="S11" s="6" t="n">
+      <c r="Q11" s="6" t="n">
         <v>0.6425466668519806</v>
       </c>
-      <c r="T11" s="4" t="inlineStr"/>
+      <c r="R11" s="4" t="inlineStr"/>
+      <c r="S11" s="3" t="n">
+        <v>4.16509397030755</v>
+      </c>
+      <c r="T11" s="3" t="n">
+        <v>7.238899784197721</v>
+      </c>
       <c r="U11" s="3" t="n">
-        <v>4.16509397030755</v>
+        <v>-11.86167353520874</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>7.238899784197721</v>
+        <v>1.575310242182038</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>-11.86167353520874</v>
+        <v>-437267300</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>1.575310242182038</v>
-      </c>
-      <c r="Y11" s="3" t="n">
-        <v>-437267300</v>
-      </c>
-      <c r="Z11" s="3" t="n">
         <v>1.1361366971018</v>
       </c>
+      <c r="Y11" s="4" t="inlineStr">
+        <is>
+          <t>−/−/−</t>
+        </is>
+      </c>
+      <c r="Z11" s="6" t="n">
+        <v>-0.3600794916801205</v>
+      </c>
       <c r="AA11" s="4" t="inlineStr">
-        <is>
-          <t>−/−/−</t>
-        </is>
-      </c>
-      <c r="AB11" s="6" t="n">
-        <v>-0.3600794916801205</v>
-      </c>
-      <c r="AC11" s="4" t="inlineStr">
         <is>
           <t>危险区</t>
         </is>
